--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-All_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Overall/Output_costs_by_tretspef-All_Raw.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>324021.28</v>
+        <v>349011.9</v>
       </c>
       <c r="C2">
-        <v>324021</v>
+        <v>287</v>
       </c>
       <c r="D2">
-        <v>279.51</v>
+        <v>251.99</v>
       </c>
       <c r="E2">
-        <v>127.49</v>
+        <v>135.31</v>
       </c>
       <c r="F2">
-        <v>4249.65</v>
+        <v>4256.88</v>
       </c>
       <c r="G2">
-        <v>1062</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>370450.61</v>
+        <v>400851.58</v>
       </c>
       <c r="C3">
-        <v>370451</v>
+        <v>320</v>
       </c>
       <c r="D3">
-        <v>354.57</v>
+        <v>287.62</v>
       </c>
       <c r="E3">
-        <v>107.61</v>
+        <v>118.14</v>
       </c>
       <c r="F3">
-        <v>5444.8</v>
+        <v>6519.05</v>
       </c>
       <c r="G3">
-        <v>1043</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>14914.56</v>
+        <v>12523.94</v>
       </c>
       <c r="C4">
-        <v>14915</v>
+        <v>737</v>
       </c>
       <c r="D4">
-        <v>1178.59</v>
+        <v>546.59</v>
       </c>
       <c r="E4">
-        <v>377.18</v>
+        <v>327.82</v>
       </c>
       <c r="F4">
-        <v>3394.66</v>
+        <v>2018.18</v>
       </c>
       <c r="G4">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>126086.17</v>
+        <v>146666.85</v>
       </c>
       <c r="C5">
-        <v>126086</v>
+        <v>238</v>
       </c>
       <c r="D5">
-        <v>184.68</v>
+        <v>142.22</v>
       </c>
       <c r="E5">
-        <v>103.63</v>
+        <v>115.53</v>
       </c>
       <c r="F5">
-        <v>2524.53</v>
+        <v>1859.53</v>
       </c>
       <c r="G5">
-        <v>550</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>16090.99</v>
+        <v>18142.03</v>
       </c>
       <c r="C6">
-        <v>16091</v>
+        <v>477</v>
       </c>
       <c r="D6">
-        <v>357.62</v>
+        <v>283.22</v>
       </c>
       <c r="E6">
-        <v>240.28</v>
+        <v>277.82</v>
       </c>
       <c r="F6">
-        <v>1469.11</v>
+        <v>1125.19</v>
       </c>
       <c r="G6">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>26847.7</v>
+        <v>27617.94</v>
       </c>
       <c r="C7">
-        <v>26848</v>
+        <v>258</v>
       </c>
       <c r="D7">
-        <v>196.93</v>
+        <v>126.34</v>
       </c>
       <c r="E7">
-        <v>128.58</v>
+        <v>141.04</v>
       </c>
       <c r="F7">
-        <v>1410.82</v>
+        <v>864.84</v>
       </c>
       <c r="G7">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>139772.49</v>
+        <v>127240.85</v>
       </c>
       <c r="C8">
-        <v>139772</v>
+        <v>303</v>
       </c>
       <c r="D8">
-        <v>309.78</v>
+        <v>200.26</v>
       </c>
       <c r="E8">
-        <v>191.26</v>
+        <v>178.71</v>
       </c>
       <c r="F8">
-        <v>2396.89</v>
+        <v>1429.71</v>
       </c>
       <c r="G8">
-        <v>350</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>87835.89</v>
+        <v>84006.77</v>
       </c>
       <c r="C9">
-        <v>87836</v>
+        <v>394</v>
       </c>
       <c r="D9">
-        <v>456.27</v>
+        <v>316.17</v>
       </c>
       <c r="E9">
-        <v>212.28</v>
+        <v>208.03</v>
       </c>
       <c r="F9">
-        <v>3225.47</v>
+        <v>2936.3</v>
       </c>
       <c r="G9">
-        <v>171</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>9290262.859999999</v>
+        <v>9540012.970000001</v>
       </c>
       <c r="C10">
-        <v>9290263</v>
+        <v>679</v>
       </c>
       <c r="D10">
-        <v>538.5</v>
+        <v>768.08</v>
       </c>
       <c r="E10">
-        <v>121.92</v>
+        <v>123.1</v>
       </c>
       <c r="F10">
-        <v>22370.78</v>
+        <v>16758.23</v>
       </c>
       <c r="G10">
-        <v>16857</v>
+        <v>14049</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>408420.11</v>
+        <v>420160.22</v>
       </c>
       <c r="C11">
-        <v>408420</v>
+        <v>287</v>
       </c>
       <c r="D11">
-        <v>766.62</v>
+        <v>246.25</v>
       </c>
       <c r="E11">
-        <v>155.43</v>
+        <v>122.09</v>
       </c>
       <c r="F11">
-        <v>24806.6</v>
+        <v>4197.79</v>
       </c>
       <c r="G11">
-        <v>1197</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>1682735.78</v>
+        <v>1780079.73</v>
       </c>
       <c r="C12">
-        <v>1682736</v>
+        <v>398</v>
       </c>
       <c r="D12">
-        <v>563.29</v>
+        <v>399.64</v>
       </c>
       <c r="E12">
-        <v>103.79</v>
+        <v>115.33</v>
       </c>
       <c r="F12">
-        <v>5510.95</v>
+        <v>7168.81</v>
       </c>
       <c r="G12">
-        <v>3331</v>
+        <v>4469</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>124006.51</v>
+        <v>149378.82</v>
       </c>
       <c r="C13">
-        <v>124007</v>
+        <v>351</v>
       </c>
       <c r="D13">
-        <v>240.31</v>
+        <v>228.54</v>
       </c>
       <c r="E13">
-        <v>141.31</v>
+        <v>156.42</v>
       </c>
       <c r="F13">
-        <v>2182.97</v>
+        <v>1684.16</v>
       </c>
       <c r="G13">
-        <v>352</v>
+        <v>425</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>86487.64999999999</v>
+        <v>101035.42</v>
       </c>
       <c r="C14">
-        <v>86488</v>
+        <v>722</v>
       </c>
       <c r="D14">
-        <v>942.72</v>
+        <v>600.51</v>
       </c>
       <c r="E14">
-        <v>242.56</v>
+        <v>278.66</v>
       </c>
       <c r="F14">
-        <v>3782.99</v>
+        <v>3172.59</v>
       </c>
       <c r="G14">
-        <v>86</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15">
@@ -723,19 +723,19 @@
         </is>
       </c>
       <c r="B15">
-        <v>708</v>
+        <v>794.51</v>
       </c>
       <c r="C15">
-        <v>708</v>
+        <v>265</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>236</v>
+        <v>264.84</v>
       </c>
       <c r="F15">
-        <v>236</v>
+        <v>264.84</v>
       </c>
       <c r="G15">
         <v>3</v>
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>99835.77</v>
+        <v>104759.37</v>
       </c>
       <c r="C16">
-        <v>99836</v>
+        <v>330</v>
       </c>
       <c r="D16">
-        <v>348.53</v>
+        <v>229.19</v>
       </c>
       <c r="E16">
-        <v>172.3</v>
+        <v>178.34</v>
       </c>
       <c r="F16">
-        <v>3091.09</v>
+        <v>2001.86</v>
       </c>
       <c r="G16">
-        <v>258</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
-        <v>166994.5</v>
+        <v>157601.83</v>
       </c>
       <c r="C17">
-        <v>166995</v>
+        <v>396</v>
       </c>
       <c r="D17">
-        <v>478.7</v>
+        <v>292.77</v>
       </c>
       <c r="E17">
-        <v>148.9</v>
+        <v>162.77</v>
       </c>
       <c r="F17">
-        <v>4967.44</v>
+        <v>3305.58</v>
       </c>
       <c r="G17">
-        <v>301</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
-        <v>155647.2</v>
+        <v>176197.02</v>
       </c>
       <c r="C18">
-        <v>155647</v>
+        <v>328</v>
       </c>
       <c r="D18">
-        <v>416.73</v>
+        <v>249.82</v>
       </c>
       <c r="E18">
-        <v>138.12</v>
+        <v>160.23</v>
       </c>
       <c r="F18">
-        <v>2789.21</v>
+        <v>1779.74</v>
       </c>
       <c r="G18">
-        <v>359</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>6790.43</v>
+        <v>7950.85</v>
       </c>
       <c r="C19">
-        <v>6790</v>
+        <v>883</v>
       </c>
       <c r="D19">
-        <v>841.79</v>
+        <v>813.55</v>
       </c>
       <c r="E19">
-        <v>166.47</v>
+        <v>163.87</v>
       </c>
       <c r="F19">
-        <v>2154.16</v>
+        <v>2336.7</v>
       </c>
       <c r="G19">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
-        <v>18997.89</v>
+        <v>18037.5</v>
       </c>
       <c r="C20">
-        <v>18998</v>
+        <v>429</v>
       </c>
       <c r="D20">
-        <v>430.3</v>
+        <v>194.42</v>
       </c>
       <c r="E20">
-        <v>302.63</v>
+        <v>319.52</v>
       </c>
       <c r="F20">
-        <v>1882.23</v>
+        <v>1228.94</v>
       </c>
       <c r="G20">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>22373.69</v>
+        <v>18453.55</v>
       </c>
       <c r="C21">
-        <v>22374</v>
+        <v>401</v>
       </c>
       <c r="D21">
-        <v>378.03</v>
+        <v>177.47</v>
       </c>
       <c r="E21">
-        <v>329.52</v>
+        <v>255.7</v>
       </c>
       <c r="F21">
-        <v>1997.3</v>
+        <v>986.78</v>
       </c>
       <c r="G21">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>11242.48</v>
+        <v>10307.25</v>
       </c>
       <c r="C22">
-        <v>11242</v>
+        <v>382</v>
       </c>
       <c r="D22">
-        <v>228.71</v>
+        <v>180.66</v>
       </c>
       <c r="E22">
-        <v>244.48</v>
+        <v>230.36</v>
       </c>
       <c r="F22">
-        <v>1084.65</v>
+        <v>1004.14</v>
       </c>
       <c r="G22">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>28144.07</v>
+        <v>31099.27</v>
       </c>
       <c r="C23">
-        <v>28144</v>
+        <v>2827</v>
       </c>
       <c r="D23">
-        <v>7938.5</v>
+        <v>2354.64</v>
       </c>
       <c r="E23">
-        <v>494.88</v>
+        <v>548.13</v>
       </c>
       <c r="F23">
-        <v>15772.09</v>
+        <v>8077.83</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>57185.68</v>
+        <v>54196.73</v>
       </c>
       <c r="C24">
-        <v>57186</v>
+        <v>186</v>
       </c>
       <c r="D24">
-        <v>198.49</v>
+        <v>128.22</v>
       </c>
       <c r="E24">
-        <v>87.86</v>
+        <v>136.09</v>
       </c>
       <c r="F24">
-        <v>1933.32</v>
+        <v>1508.35</v>
       </c>
       <c r="G24">
-        <v>269</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>51384.67</v>
+        <v>80076.60000000001</v>
       </c>
       <c r="C25">
-        <v>51385</v>
+        <v>199</v>
       </c>
       <c r="D25">
-        <v>65.95</v>
+        <v>89.08</v>
       </c>
       <c r="E25">
-        <v>104.19</v>
+        <v>89.19</v>
       </c>
       <c r="F25">
-        <v>531.72</v>
+        <v>773.96</v>
       </c>
       <c r="G25">
-        <v>374</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>260839.25</v>
+        <v>283870.66</v>
       </c>
       <c r="C26">
-        <v>260839</v>
+        <v>426</v>
       </c>
       <c r="D26">
-        <v>482.94</v>
+        <v>348.37</v>
       </c>
       <c r="E26">
-        <v>177.52</v>
+        <v>179.65</v>
       </c>
       <c r="F26">
-        <v>3276.97</v>
+        <v>3157.31</v>
       </c>
       <c r="G26">
-        <v>481</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>2246.51</v>
+        <v>3307.88</v>
       </c>
       <c r="C27">
-        <v>2247</v>
+        <v>301</v>
       </c>
       <c r="D27">
-        <v>111.63</v>
+        <v>86.83</v>
       </c>
       <c r="E27">
-        <v>149.12</v>
+        <v>191.54</v>
       </c>
       <c r="F27">
-        <v>523.54</v>
+        <v>383.07</v>
       </c>
       <c r="G27">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1048,19 +1048,19 @@
         </is>
       </c>
       <c r="B28">
-        <v>2949.13</v>
+        <v>3696.35</v>
       </c>
       <c r="C28">
-        <v>2949</v>
+        <v>246</v>
       </c>
       <c r="D28">
-        <v>101.4</v>
+        <v>124.18</v>
       </c>
       <c r="E28">
-        <v>159.93</v>
+        <v>201.64</v>
       </c>
       <c r="F28">
-        <v>514.98</v>
+        <v>638.35</v>
       </c>
       <c r="G28">
         <v>15</v>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>153.51</v>
+        <v>169.53</v>
       </c>
       <c r="C29">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E29">
-        <v>153.51</v>
+        <v>169.53</v>
       </c>
       <c r="F29">
-        <v>153.51</v>
+        <v>169.53</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1095,22 +1095,22 @@
         </is>
       </c>
       <c r="B30">
-        <v>1929.35</v>
+        <v>2380.26</v>
       </c>
       <c r="C30">
-        <v>1929</v>
+        <v>216</v>
       </c>
       <c r="D30">
-        <v>257.82</v>
+        <v>154.08</v>
       </c>
       <c r="E30">
-        <v>120.58</v>
+        <v>148.77</v>
       </c>
       <c r="F30">
-        <v>844.09</v>
+        <v>595.0700000000001</v>
       </c>
       <c r="G30">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>481708.93</v>
+        <v>745208.04</v>
       </c>
       <c r="C31">
-        <v>481709</v>
+        <v>424</v>
       </c>
       <c r="D31">
-        <v>1319.4</v>
+        <v>493.17</v>
       </c>
       <c r="E31">
-        <v>123.17</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F31">
-        <v>24971.1</v>
+        <v>5368.73</v>
       </c>
       <c r="G31">
-        <v>1141</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="32">
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>310662.76</v>
+        <v>377300.7</v>
       </c>
       <c r="C32">
-        <v>310663</v>
+        <v>323</v>
       </c>
       <c r="D32">
-        <v>266.95</v>
+        <v>221.8</v>
       </c>
       <c r="E32">
-        <v>124.55</v>
+        <v>133.83</v>
       </c>
       <c r="F32">
-        <v>3051.76</v>
+        <v>2136.2</v>
       </c>
       <c r="G32">
-        <v>957</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="33">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>137231.1</v>
+        <v>141023.22</v>
       </c>
       <c r="C33">
-        <v>137231</v>
+        <v>394</v>
       </c>
       <c r="D33">
-        <v>370.19</v>
+        <v>256.09</v>
       </c>
       <c r="E33">
-        <v>152.31</v>
+        <v>153.58</v>
       </c>
       <c r="F33">
-        <v>3184.03</v>
+        <v>2306.41</v>
       </c>
       <c r="G33">
-        <v>273</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34">
@@ -1195,22 +1195,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>340819.34</v>
+        <v>349025.57</v>
       </c>
       <c r="C34">
-        <v>340819</v>
+        <v>462</v>
       </c>
       <c r="D34">
-        <v>819.87</v>
+        <v>403.71</v>
       </c>
       <c r="E34">
-        <v>167.97</v>
+        <v>151.13</v>
       </c>
       <c r="F34">
-        <v>6863.98</v>
+        <v>4726.96</v>
       </c>
       <c r="G34">
-        <v>476</v>
+        <v>755</v>
       </c>
     </row>
     <row r="35">
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="B35">
-        <v>62068.59</v>
+        <v>63083.7</v>
       </c>
       <c r="C35">
-        <v>62069</v>
+        <v>116</v>
       </c>
       <c r="D35">
-        <v>82.48999999999999</v>
+        <v>64.58</v>
       </c>
       <c r="E35">
-        <v>67.56999999999999</v>
+        <v>62.34</v>
       </c>
       <c r="F35">
-        <v>743.28</v>
+        <v>548.9400000000001</v>
       </c>
       <c r="G35">
-        <v>503</v>
+        <v>543</v>
       </c>
     </row>
     <row r="36">
@@ -1245,22 +1245,22 @@
         </is>
       </c>
       <c r="B36">
-        <v>5083.33</v>
+        <v>6396.94</v>
       </c>
       <c r="C36">
-        <v>5083</v>
+        <v>582</v>
       </c>
       <c r="D36">
-        <v>621.99</v>
+        <v>344.36</v>
       </c>
       <c r="E36">
-        <v>288.17</v>
+        <v>328.83</v>
       </c>
       <c r="F36">
-        <v>2017.19</v>
+        <v>1315.32</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1270,22 +1270,22 @@
         </is>
       </c>
       <c r="B37">
-        <v>30245.87</v>
+        <v>27930.75</v>
       </c>
       <c r="C37">
-        <v>30246</v>
+        <v>317</v>
       </c>
       <c r="D37">
-        <v>231.57</v>
+        <v>170.58</v>
       </c>
       <c r="E37">
-        <v>200.45</v>
+        <v>183.18</v>
       </c>
       <c r="F37">
-        <v>1038.03</v>
+        <v>774.22</v>
       </c>
       <c r="G37">
-        <v>71</v>
+        <v>88</v>
       </c>
     </row>
     <row r="38">
@@ -1295,22 +1295,22 @@
         </is>
       </c>
       <c r="B38">
-        <v>191000.6</v>
+        <v>214771</v>
       </c>
       <c r="C38">
-        <v>191001</v>
+        <v>519</v>
       </c>
       <c r="D38">
-        <v>1059.76</v>
+        <v>525.95</v>
       </c>
       <c r="E38">
-        <v>149.27</v>
+        <v>159.59</v>
       </c>
       <c r="F38">
-        <v>11311.42</v>
+        <v>4694.67</v>
       </c>
       <c r="G38">
-        <v>265</v>
+        <v>414</v>
       </c>
     </row>
     <row r="39">
@@ -1320,16 +1320,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>414.21</v>
+        <v>391.93</v>
       </c>
       <c r="C39">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="E39">
-        <v>414.21</v>
+        <v>391.93</v>
       </c>
       <c r="F39">
-        <v>414.21</v>
+        <v>391.93</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1342,22 +1342,22 @@
         </is>
       </c>
       <c r="B40">
-        <v>10760.16</v>
+        <v>7913.97</v>
       </c>
       <c r="C40">
-        <v>10760</v>
+        <v>989</v>
       </c>
       <c r="D40">
-        <v>860.42</v>
+        <v>680.6900000000001</v>
       </c>
       <c r="E40">
-        <v>775.21</v>
+        <v>301.07</v>
       </c>
       <c r="F40">
-        <v>3201.06</v>
+        <v>2333.38</v>
       </c>
       <c r="G40">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
@@ -1367,22 +1367,22 @@
         </is>
       </c>
       <c r="B41">
-        <v>93981.14999999999</v>
+        <v>117485.32</v>
       </c>
       <c r="C41">
-        <v>93981</v>
+        <v>366</v>
       </c>
       <c r="D41">
-        <v>265.63</v>
+        <v>220.99</v>
       </c>
       <c r="E41">
-        <v>164.13</v>
+        <v>134.67</v>
       </c>
       <c r="F41">
-        <v>1497.79</v>
+        <v>1267.02</v>
       </c>
       <c r="G41">
-        <v>248</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42">
@@ -1392,19 +1392,19 @@
         </is>
       </c>
       <c r="B42">
-        <v>5856.26</v>
+        <v>5200.31</v>
       </c>
       <c r="C42">
-        <v>5856</v>
+        <v>520</v>
       </c>
       <c r="D42">
-        <v>110.18</v>
+        <v>62.59</v>
       </c>
       <c r="E42">
-        <v>401.11</v>
+        <v>418.92</v>
       </c>
       <c r="F42">
-        <v>668.85</v>
+        <v>566.27</v>
       </c>
       <c r="G42">
         <v>10</v>
@@ -1417,22 +1417,22 @@
         </is>
       </c>
       <c r="B43">
-        <v>9689.52</v>
+        <v>13262.69</v>
       </c>
       <c r="C43">
-        <v>9690</v>
+        <v>428</v>
       </c>
       <c r="D43">
-        <v>360.13</v>
+        <v>218.13</v>
       </c>
       <c r="E43">
-        <v>204.36</v>
+        <v>276.01</v>
       </c>
       <c r="F43">
-        <v>1430.55</v>
+        <v>967.8200000000001</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="B44">
-        <v>222028.46</v>
+        <v>429428.62</v>
       </c>
       <c r="C44">
-        <v>222028</v>
+        <v>850</v>
       </c>
       <c r="D44">
-        <v>906.01</v>
+        <v>1049.74</v>
       </c>
       <c r="E44">
-        <v>140.16</v>
+        <v>214.09</v>
       </c>
       <c r="F44">
-        <v>9396.51</v>
+        <v>13578.28</v>
       </c>
       <c r="G44">
-        <v>317</v>
+        <v>505</v>
       </c>
     </row>
     <row r="45">
@@ -1467,22 +1467,22 @@
         </is>
       </c>
       <c r="B45">
-        <v>57150.16</v>
+        <v>58013.42</v>
       </c>
       <c r="C45">
-        <v>57150</v>
+        <v>879</v>
       </c>
       <c r="D45">
-        <v>3179.68</v>
+        <v>803.67</v>
       </c>
       <c r="E45">
-        <v>110.98</v>
+        <v>175.54</v>
       </c>
       <c r="F45">
-        <v>16429.55</v>
+        <v>3715.5</v>
       </c>
       <c r="G45">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="B46">
-        <v>14267.72</v>
+        <v>13186.16</v>
       </c>
       <c r="C46">
-        <v>14268</v>
+        <v>733</v>
       </c>
       <c r="D46">
-        <v>727.88</v>
+        <v>563.35</v>
       </c>
       <c r="E46">
-        <v>532.25</v>
+        <v>319.54</v>
       </c>
       <c r="F46">
-        <v>2339.1</v>
+        <v>2236.77</v>
       </c>
       <c r="G46">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
@@ -1517,22 +1517,22 @@
         </is>
       </c>
       <c r="B47">
-        <v>17963.87</v>
+        <v>19566.93</v>
       </c>
       <c r="C47">
-        <v>17964</v>
+        <v>652</v>
       </c>
       <c r="D47">
-        <v>2583.54</v>
+        <v>729.24</v>
       </c>
       <c r="E47">
-        <v>201.51</v>
+        <v>217</v>
       </c>
       <c r="F47">
-        <v>10478.61</v>
+        <v>3254.99</v>
       </c>
       <c r="G47">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1542,22 +1542,22 @@
         </is>
       </c>
       <c r="B48">
-        <v>149479.03</v>
+        <v>255273.43</v>
       </c>
       <c r="C48">
-        <v>149479</v>
+        <v>493</v>
       </c>
       <c r="D48">
-        <v>1747.12</v>
+        <v>551.13</v>
       </c>
       <c r="E48">
-        <v>81.75</v>
+        <v>80.09</v>
       </c>
       <c r="F48">
-        <v>10120.5</v>
+        <v>4371.81</v>
       </c>
       <c r="G48">
-        <v>136</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49">
@@ -1567,22 +1567,22 @@
         </is>
       </c>
       <c r="B49">
-        <v>742434.08</v>
+        <v>771905.26</v>
       </c>
       <c r="C49">
-        <v>742434</v>
+        <v>312</v>
       </c>
       <c r="D49">
-        <v>345.24</v>
+        <v>238.01</v>
       </c>
       <c r="E49">
-        <v>144.39</v>
+        <v>135.62</v>
       </c>
       <c r="F49">
-        <v>4868.93</v>
+        <v>2404.21</v>
       </c>
       <c r="G49">
-        <v>2020</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="50">
@@ -1592,19 +1592,19 @@
         </is>
       </c>
       <c r="B50">
-        <v>928.51</v>
+        <v>1111.02</v>
       </c>
       <c r="C50">
-        <v>929</v>
+        <v>159</v>
       </c>
       <c r="D50">
-        <v>73.92</v>
+        <v>89.94</v>
       </c>
       <c r="E50">
-        <v>32.54</v>
+        <v>28.91</v>
       </c>
       <c r="F50">
-        <v>248.4</v>
+        <v>292.21</v>
       </c>
       <c r="G50">
         <v>7</v>
@@ -1617,22 +1617,22 @@
         </is>
       </c>
       <c r="B51">
-        <v>13028.32</v>
+        <v>12129.68</v>
       </c>
       <c r="C51">
-        <v>13028</v>
+        <v>758</v>
       </c>
       <c r="D51">
-        <v>1042.48</v>
+        <v>343.1</v>
       </c>
       <c r="E51">
-        <v>303.16</v>
+        <v>246.97</v>
       </c>
       <c r="F51">
-        <v>3898.47</v>
+        <v>1411.81</v>
       </c>
       <c r="G51">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="B52">
-        <v>197049.21</v>
+        <v>221316.03</v>
       </c>
       <c r="C52">
-        <v>197049</v>
+        <v>282</v>
       </c>
       <c r="D52">
-        <v>760.0599999999999</v>
+        <v>299.33</v>
       </c>
       <c r="E52">
-        <v>65.18000000000001</v>
+        <v>65.73</v>
       </c>
       <c r="F52">
-        <v>3538.61</v>
+        <v>2679.7</v>
       </c>
       <c r="G52">
-        <v>299</v>
+        <v>784</v>
       </c>
     </row>
     <row r="53">
@@ -1667,16 +1667,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>757.1799999999999</v>
+        <v>590.53</v>
       </c>
       <c r="C53">
-        <v>757</v>
+        <v>591</v>
       </c>
       <c r="E53">
-        <v>757.1799999999999</v>
+        <v>590.53</v>
       </c>
       <c r="F53">
-        <v>757.1799999999999</v>
+        <v>590.53</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -1689,22 +1689,22 @@
         </is>
       </c>
       <c r="B54">
-        <v>14664.27</v>
+        <v>11632.03</v>
       </c>
       <c r="C54">
-        <v>14664</v>
+        <v>554</v>
       </c>
       <c r="D54">
-        <v>1129.91</v>
+        <v>674.79</v>
       </c>
       <c r="E54">
-        <v>132.35</v>
+        <v>112.19</v>
       </c>
       <c r="F54">
-        <v>3551.9</v>
+        <v>2821.45</v>
       </c>
       <c r="G54">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -1714,22 +1714,22 @@
         </is>
       </c>
       <c r="B55">
-        <v>26568.72</v>
+        <v>23572.98</v>
       </c>
       <c r="C55">
-        <v>26569</v>
+        <v>363</v>
       </c>
       <c r="D55">
-        <v>225.04</v>
+        <v>204.41</v>
       </c>
       <c r="E55">
-        <v>304.53</v>
+        <v>294.06</v>
       </c>
       <c r="F55">
-        <v>1827.15</v>
+        <v>1764.35</v>
       </c>
       <c r="G55">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -1739,22 +1739,22 @@
         </is>
       </c>
       <c r="B56">
-        <v>43772.94</v>
+        <v>43366.65</v>
       </c>
       <c r="C56">
-        <v>43773</v>
+        <v>344</v>
       </c>
       <c r="D56">
-        <v>123.19</v>
+        <v>97.2</v>
       </c>
       <c r="E56">
-        <v>215.48</v>
+        <v>248.29</v>
       </c>
       <c r="F56">
-        <v>979.5599999999999</v>
+        <v>817.28</v>
       </c>
       <c r="G56">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57">
@@ -1764,22 +1764,22 @@
         </is>
       </c>
       <c r="B57">
-        <v>453150.07</v>
+        <v>490498.25</v>
       </c>
       <c r="C57">
-        <v>453150</v>
+        <v>342</v>
       </c>
       <c r="D57">
-        <v>662.7</v>
+        <v>316.01</v>
       </c>
       <c r="E57">
-        <v>116.72</v>
+        <v>102.92</v>
       </c>
       <c r="F57">
-        <v>10913.61</v>
+        <v>3534.92</v>
       </c>
       <c r="G57">
-        <v>1116</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="58">
@@ -1789,22 +1789,22 @@
         </is>
       </c>
       <c r="B58">
-        <v>1636.79</v>
+        <v>1280.43</v>
       </c>
       <c r="C58">
-        <v>1637</v>
+        <v>427</v>
       </c>
       <c r="D58">
-        <v>768.46</v>
+        <v>373.06</v>
       </c>
       <c r="E58">
-        <v>275.01</v>
+        <v>211.42</v>
       </c>
       <c r="F58">
-        <v>1361.77</v>
+        <v>857.59</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1814,22 +1814,22 @@
         </is>
       </c>
       <c r="B59">
-        <v>502484.17</v>
+        <v>538049.26</v>
       </c>
       <c r="C59">
-        <v>502484</v>
+        <v>444</v>
       </c>
       <c r="D59">
-        <v>727.48</v>
+        <v>445.08</v>
       </c>
       <c r="E59">
-        <v>144.52</v>
+        <v>153.41</v>
       </c>
       <c r="F59">
-        <v>10739.52</v>
+        <v>6855.61</v>
       </c>
       <c r="G59">
-        <v>868</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="60">
@@ -1839,22 +1839,22 @@
         </is>
       </c>
       <c r="B60">
-        <v>33104.19</v>
+        <v>32064.89</v>
       </c>
       <c r="C60">
-        <v>33104</v>
+        <v>217</v>
       </c>
       <c r="D60">
-        <v>224.77</v>
+        <v>156.91</v>
       </c>
       <c r="E60">
-        <v>146.44</v>
+        <v>138.05</v>
       </c>
       <c r="F60">
-        <v>1474.16</v>
+        <v>1163.14</v>
       </c>
       <c r="G60">
-        <v>123</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61">
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B61">
-        <v>728.3200000000001</v>
+        <v>782.99</v>
       </c>
       <c r="C61">
-        <v>728</v>
+        <v>130</v>
       </c>
       <c r="D61">
-        <v>51.17</v>
+        <v>90.47</v>
       </c>
       <c r="E61">
-        <v>49.88</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="F61">
-        <v>199.5</v>
+        <v>303.96</v>
       </c>
       <c r="G61">
         <v>6</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B62">
-        <v>652.08</v>
+        <v>1101.14</v>
       </c>
       <c r="C62">
-        <v>652</v>
+        <v>551</v>
       </c>
       <c r="D62">
-        <v>230.55</v>
+        <v>389.31</v>
       </c>
       <c r="E62">
-        <v>163.02</v>
+        <v>275.29</v>
       </c>
       <c r="F62">
-        <v>489.06</v>
+        <v>825.86</v>
       </c>
       <c r="G62">
         <v>2</v>
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="B63">
-        <v>854.86</v>
+        <v>804.02</v>
       </c>
       <c r="C63">
-        <v>855</v>
+        <v>268</v>
       </c>
       <c r="D63">
-        <v>230.9</v>
+        <v>128.38</v>
       </c>
       <c r="E63">
-        <v>264.16</v>
+        <v>146.1</v>
       </c>
       <c r="F63">
-        <v>590.7</v>
+        <v>402.01</v>
       </c>
       <c r="G63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -1939,22 +1939,22 @@
         </is>
       </c>
       <c r="B64">
-        <v>9656.799999999999</v>
+        <v>17786.12</v>
       </c>
       <c r="C64">
-        <v>9657</v>
+        <v>508</v>
       </c>
       <c r="D64">
-        <v>386.46</v>
+        <v>373.12</v>
       </c>
       <c r="E64">
-        <v>117.07</v>
+        <v>288.24</v>
       </c>
       <c r="F64">
-        <v>1469.9</v>
+        <v>2088.89</v>
       </c>
       <c r="G64">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65">
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B65">
-        <v>478.8</v>
+        <v>1120.15</v>
       </c>
       <c r="C65">
-        <v>479</v>
+        <v>373</v>
       </c>
       <c r="D65">
-        <v>12.56</v>
+        <v>143.2</v>
       </c>
       <c r="E65">
-        <v>145.1</v>
+        <v>208.03</v>
       </c>
       <c r="F65">
-        <v>166.85</v>
+        <v>456.06</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -1989,22 +1989,22 @@
         </is>
       </c>
       <c r="B66">
-        <v>1354.66</v>
+        <v>2120.42</v>
       </c>
       <c r="C66">
-        <v>1355</v>
+        <v>353</v>
       </c>
       <c r="D66">
-        <v>156.02</v>
+        <v>205.92</v>
       </c>
       <c r="E66">
-        <v>134.99</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="F66">
-        <v>526.51</v>
+        <v>639.63</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
@@ -2014,22 +2014,22 @@
         </is>
       </c>
       <c r="B67">
-        <v>205899.05</v>
+        <v>219309.67</v>
       </c>
       <c r="C67">
-        <v>205899</v>
+        <v>503</v>
       </c>
       <c r="D67">
-        <v>804.22</v>
+        <v>466.25</v>
       </c>
       <c r="E67">
-        <v>149.59</v>
+        <v>161.37</v>
       </c>
       <c r="F67">
-        <v>5337.22</v>
+        <v>3203.97</v>
       </c>
       <c r="G67">
-        <v>265</v>
+        <v>436</v>
       </c>
     </row>
     <row r="68">
@@ -2039,22 +2039,22 @@
         </is>
       </c>
       <c r="B68">
-        <v>84584.64</v>
+        <v>75369.83</v>
       </c>
       <c r="C68">
-        <v>84585</v>
+        <v>580</v>
       </c>
       <c r="D68">
-        <v>2026.18</v>
+        <v>654.9299999999999</v>
       </c>
       <c r="E68">
-        <v>173.28</v>
+        <v>153.46</v>
       </c>
       <c r="F68">
-        <v>10302.17</v>
+        <v>3808.74</v>
       </c>
       <c r="G68">
-        <v>73</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69">
@@ -2064,22 +2064,22 @@
         </is>
       </c>
       <c r="B69">
-        <v>6287.66</v>
+        <v>11206.76</v>
       </c>
       <c r="C69">
-        <v>6288</v>
+        <v>340</v>
       </c>
       <c r="D69">
-        <v>175.08</v>
+        <v>241.41</v>
       </c>
       <c r="E69">
-        <v>100.91</v>
+        <v>60.17</v>
       </c>
       <c r="F69">
-        <v>940.6799999999999</v>
+        <v>964.1</v>
       </c>
       <c r="G69">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -2089,22 +2089,22 @@
         </is>
       </c>
       <c r="B70">
-        <v>415568.56</v>
+        <v>428837.51</v>
       </c>
       <c r="C70">
-        <v>415569</v>
+        <v>433</v>
       </c>
       <c r="D70">
-        <v>515.4299999999999</v>
+        <v>334.95</v>
       </c>
       <c r="E70">
-        <v>154.01</v>
+        <v>178</v>
       </c>
       <c r="F70">
-        <v>5818.51</v>
+        <v>3800.09</v>
       </c>
       <c r="G70">
-        <v>765</v>
+        <v>991</v>
       </c>
     </row>
     <row r="71">
@@ -2114,22 +2114,22 @@
         </is>
       </c>
       <c r="B71">
-        <v>81792.83</v>
+        <v>100738.93</v>
       </c>
       <c r="C71">
-        <v>81793</v>
+        <v>431</v>
       </c>
       <c r="D71">
-        <v>160.18</v>
+        <v>154.28</v>
       </c>
       <c r="E71">
-        <v>312.93</v>
+        <v>374.01</v>
       </c>
       <c r="F71">
-        <v>1564.63</v>
+        <v>1490.01</v>
       </c>
       <c r="G71">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72">
@@ -2139,22 +2139,22 @@
         </is>
       </c>
       <c r="B72">
-        <v>1056472.09</v>
+        <v>1158629.99</v>
       </c>
       <c r="C72">
-        <v>1056472</v>
+        <v>438</v>
       </c>
       <c r="D72">
-        <v>496.46</v>
+        <v>353.93</v>
       </c>
       <c r="E72">
-        <v>119.26</v>
+        <v>129.85</v>
       </c>
       <c r="F72">
-        <v>10426.97</v>
+        <v>3564.42</v>
       </c>
       <c r="G72">
-        <v>2193</v>
+        <v>2647</v>
       </c>
     </row>
     <row r="73">
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B73">
-        <v>646.83</v>
+        <v>708.53</v>
       </c>
       <c r="C73">
-        <v>647</v>
+        <v>354</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>323.42</v>
+        <v>354.27</v>
       </c>
       <c r="F73">
-        <v>323.42</v>
+        <v>354.27</v>
       </c>
       <c r="G73">
         <v>2</v>
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="B74">
-        <v>1324961.73</v>
+        <v>1277010.91</v>
       </c>
       <c r="C74">
-        <v>1324962</v>
+        <v>761</v>
       </c>
       <c r="D74">
-        <v>1551.61</v>
+        <v>687.71</v>
       </c>
       <c r="E74">
-        <v>242.38</v>
+        <v>234.68</v>
       </c>
       <c r="F74">
-        <v>32491.29</v>
+        <v>10236.63</v>
       </c>
       <c r="G74">
-        <v>1374</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="75">
@@ -2214,22 +2214,22 @@
         </is>
       </c>
       <c r="B75">
-        <v>25795.87</v>
+        <v>26546.11</v>
       </c>
       <c r="C75">
-        <v>25796</v>
+        <v>320</v>
       </c>
       <c r="D75">
-        <v>412.87</v>
+        <v>239.08</v>
       </c>
       <c r="E75">
-        <v>194.67</v>
+        <v>196.58</v>
       </c>
       <c r="F75">
-        <v>2530.72</v>
+        <v>1572.66</v>
       </c>
       <c r="G75">
-        <v>59</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
@@ -2239,22 +2239,22 @@
         </is>
       </c>
       <c r="B76">
-        <v>15759.99</v>
+        <v>11440.9</v>
       </c>
       <c r="C76">
-        <v>15760</v>
+        <v>153</v>
       </c>
       <c r="D76">
-        <v>434.08</v>
+        <v>243.01</v>
       </c>
       <c r="E76">
-        <v>115.35</v>
+        <v>82.33</v>
       </c>
       <c r="F76">
-        <v>3345.16</v>
+        <v>2140.61</v>
       </c>
       <c r="G76">
-        <v>58</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B77">
-        <v>1223.49</v>
+        <v>1207.73</v>
       </c>
       <c r="C77">
-        <v>1223</v>
+        <v>242</v>
       </c>
       <c r="D77">
-        <v>108.21</v>
+        <v>98.13</v>
       </c>
       <c r="E77">
-        <v>180.96</v>
+        <v>189.08</v>
       </c>
       <c r="F77">
-        <v>430.78</v>
+        <v>414.78</v>
       </c>
       <c r="G77">
         <v>5</v>
@@ -2289,22 +2289,22 @@
         </is>
       </c>
       <c r="B78">
-        <v>381215.38</v>
+        <v>427041.46</v>
       </c>
       <c r="C78">
-        <v>381215</v>
+        <v>373</v>
       </c>
       <c r="D78">
-        <v>321.64</v>
+        <v>248.8</v>
       </c>
       <c r="E78">
-        <v>132.89</v>
+        <v>159.7</v>
       </c>
       <c r="F78">
-        <v>3926.25</v>
+        <v>2253.76</v>
       </c>
       <c r="G78">
-        <v>904</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="79">
@@ -2314,22 +2314,22 @@
         </is>
       </c>
       <c r="B79">
-        <v>34532.98</v>
+        <v>40640.82</v>
       </c>
       <c r="C79">
-        <v>34533</v>
+        <v>288</v>
       </c>
       <c r="D79">
-        <v>266.46</v>
+        <v>225.43</v>
       </c>
       <c r="E79">
-        <v>122.66</v>
+        <v>150.42</v>
       </c>
       <c r="F79">
-        <v>2240.9</v>
+        <v>2175.49</v>
       </c>
       <c r="G79">
-        <v>117</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80">
@@ -2339,22 +2339,22 @@
         </is>
       </c>
       <c r="B80">
-        <v>2790194.28</v>
+        <v>2922688.14</v>
       </c>
       <c r="C80">
-        <v>2790194</v>
+        <v>368</v>
       </c>
       <c r="D80">
-        <v>505.85</v>
+        <v>366.73</v>
       </c>
       <c r="E80">
-        <v>81.45999999999999</v>
+        <v>90.05</v>
       </c>
       <c r="F80">
-        <v>10790.58</v>
+        <v>6585.97</v>
       </c>
       <c r="G80">
-        <v>5425</v>
+        <v>7937</v>
       </c>
     </row>
     <row r="81">
@@ -2364,22 +2364,22 @@
         </is>
       </c>
       <c r="B81">
-        <v>288586.38</v>
+        <v>384202.89</v>
       </c>
       <c r="C81">
-        <v>288586</v>
+        <v>369</v>
       </c>
       <c r="D81">
-        <v>686.14</v>
+        <v>425.75</v>
       </c>
       <c r="E81">
-        <v>100.68</v>
+        <v>131.74</v>
       </c>
       <c r="F81">
-        <v>8473.68</v>
+        <v>6350.35</v>
       </c>
       <c r="G81">
-        <v>621</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="82">
@@ -2389,22 +2389,22 @@
         </is>
       </c>
       <c r="B82">
-        <v>43222.31</v>
+        <v>53331.43</v>
       </c>
       <c r="C82">
-        <v>43222</v>
+        <v>417</v>
       </c>
       <c r="D82">
-        <v>537.88</v>
+        <v>278.58</v>
       </c>
       <c r="E82">
-        <v>131.97</v>
+        <v>225.82</v>
       </c>
       <c r="F82">
-        <v>4253.5</v>
+        <v>2258.17</v>
       </c>
       <c r="G82">
-        <v>88</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83">
@@ -2414,22 +2414,22 @@
         </is>
       </c>
       <c r="B83">
-        <v>138400.75</v>
+        <v>146677.13</v>
       </c>
       <c r="C83">
-        <v>138401</v>
+        <v>231</v>
       </c>
       <c r="D83">
-        <v>411.36</v>
+        <v>212.51</v>
       </c>
       <c r="E83">
-        <v>90.98999999999999</v>
+        <v>93.91</v>
       </c>
       <c r="F83">
-        <v>2911.6</v>
+        <v>2065.95</v>
       </c>
       <c r="G83">
-        <v>372</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="B84">
-        <v>66870.45</v>
+        <v>95600.86</v>
       </c>
       <c r="C84">
-        <v>66870</v>
+        <v>308</v>
       </c>
       <c r="D84">
-        <v>348.98</v>
+        <v>269.71</v>
       </c>
       <c r="E84">
-        <v>93.48</v>
+        <v>126.62</v>
       </c>
       <c r="F84">
-        <v>3673.88</v>
+        <v>2428.13</v>
       </c>
       <c r="G84">
-        <v>226</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85">
@@ -2464,22 +2464,22 @@
         </is>
       </c>
       <c r="B85">
-        <v>35036.35</v>
+        <v>35563.02</v>
       </c>
       <c r="C85">
-        <v>35036</v>
+        <v>159</v>
       </c>
       <c r="D85">
-        <v>140.37</v>
+        <v>103.67</v>
       </c>
       <c r="E85">
-        <v>107.33</v>
+        <v>106.73</v>
       </c>
       <c r="F85">
-        <v>858.62</v>
+        <v>747.09</v>
       </c>
       <c r="G85">
-        <v>178</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86">
@@ -2489,22 +2489,22 @@
         </is>
       </c>
       <c r="B86">
-        <v>23280.59</v>
+        <v>32000.13</v>
       </c>
       <c r="C86">
-        <v>23281</v>
+        <v>842</v>
       </c>
       <c r="D86">
-        <v>1767.17</v>
+        <v>783.64</v>
       </c>
       <c r="E86">
-        <v>227.43</v>
+        <v>312.16</v>
       </c>
       <c r="F86">
-        <v>8104.01</v>
+        <v>3194.56</v>
       </c>
       <c r="G86">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87">
@@ -2514,19 +2514,19 @@
         </is>
       </c>
       <c r="B87">
-        <v>1385.38</v>
+        <v>744.99</v>
       </c>
       <c r="C87">
-        <v>1385</v>
+        <v>186</v>
       </c>
       <c r="D87">
-        <v>144.16</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="E87">
-        <v>163.7</v>
+        <v>105.65</v>
       </c>
       <c r="F87">
-        <v>461.79</v>
+        <v>248.33</v>
       </c>
       <c r="G87">
         <v>4</v>
@@ -2539,22 +2539,22 @@
         </is>
       </c>
       <c r="B88">
-        <v>85063.42</v>
+        <v>91158.05</v>
       </c>
       <c r="C88">
-        <v>85063</v>
+        <v>295</v>
       </c>
       <c r="D88">
-        <v>257.65</v>
+        <v>193.45</v>
       </c>
       <c r="E88">
-        <v>173.2</v>
+        <v>174.83</v>
       </c>
       <c r="F88">
-        <v>2078.44</v>
+        <v>1748.32</v>
       </c>
       <c r="G88">
-        <v>255</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89">
@@ -2564,22 +2564,22 @@
         </is>
       </c>
       <c r="B89">
-        <v>7854.31</v>
+        <v>7928.1</v>
       </c>
       <c r="C89">
-        <v>7854</v>
+        <v>180</v>
       </c>
       <c r="D89">
-        <v>114.84</v>
+        <v>115.42</v>
       </c>
       <c r="E89">
-        <v>133.52</v>
+        <v>123.76</v>
       </c>
       <c r="F89">
-        <v>534.0700000000001</v>
+        <v>589.51</v>
       </c>
       <c r="G89">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="90">
@@ -2589,22 +2589,22 @@
         </is>
       </c>
       <c r="B90">
-        <v>6640.62</v>
+        <v>7125</v>
       </c>
       <c r="C90">
-        <v>6641</v>
+        <v>324</v>
       </c>
       <c r="D90">
-        <v>352.83</v>
+        <v>185.51</v>
       </c>
       <c r="E90">
-        <v>147.22</v>
+        <v>160.99</v>
       </c>
       <c r="F90">
-        <v>1365.71</v>
+        <v>804.9400000000001</v>
       </c>
       <c r="G90">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -2614,23 +2614,22 @@
         </is>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>2305.23</v>
       </c>
       <c r="C91">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="D91">
+        <v>32.87</v>
+      </c>
+      <c r="E91">
+        <v>12.88</v>
+      </c>
+      <c r="F91">
+        <v>141.66</v>
       </c>
       <c r="G91">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="92">
@@ -2640,22 +2639,22 @@
         </is>
       </c>
       <c r="B92">
-        <v>283949.93</v>
+        <v>464415.12</v>
       </c>
       <c r="C92">
-        <v>283950</v>
+        <v>1433</v>
       </c>
       <c r="D92">
-        <v>3678.01</v>
+        <v>1497.33</v>
       </c>
       <c r="E92">
-        <v>230.43</v>
+        <v>421.37</v>
       </c>
       <c r="F92">
-        <v>40814.45</v>
+        <v>9104.690000000001</v>
       </c>
       <c r="G92">
-        <v>195</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -2665,16 +2664,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>1489.76</v>
+        <v>1109.23</v>
       </c>
       <c r="C93">
-        <v>1490</v>
+        <v>1109</v>
       </c>
       <c r="E93">
-        <v>1489.76</v>
+        <v>1109.23</v>
       </c>
       <c r="F93">
-        <v>1489.76</v>
+        <v>1109.23</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -2687,19 +2686,19 @@
         </is>
       </c>
       <c r="B94">
-        <v>2045.36</v>
+        <v>7804.9</v>
       </c>
       <c r="C94">
-        <v>2045</v>
+        <v>2602</v>
       </c>
       <c r="D94">
-        <v>638.8099999999999</v>
+        <v>1384.1</v>
       </c>
       <c r="E94">
-        <v>312.97</v>
+        <v>1802.52</v>
       </c>
       <c r="F94">
-        <v>1419.42</v>
+        <v>4199.86</v>
       </c>
       <c r="G94">
         <v>3</v>
@@ -2712,22 +2711,22 @@
         </is>
       </c>
       <c r="B95">
-        <v>757746.66</v>
+        <v>483091.66</v>
       </c>
       <c r="C95">
-        <v>757747</v>
+        <v>757</v>
       </c>
       <c r="D95">
-        <v>2890.89</v>
+        <v>853.3099999999999</v>
       </c>
       <c r="E95">
-        <v>520.21</v>
+        <v>281.6</v>
       </c>
       <c r="F95">
-        <v>33305.45</v>
+        <v>7962.02</v>
       </c>
       <c r="G95">
-        <v>473</v>
+        <v>638</v>
       </c>
     </row>
     <row r="96">
@@ -2737,22 +2736,22 @@
         </is>
       </c>
       <c r="B96">
-        <v>24241.51</v>
+        <v>30939.02</v>
       </c>
       <c r="C96">
-        <v>24242</v>
+        <v>658</v>
       </c>
       <c r="D96">
-        <v>840.45</v>
+        <v>708.54</v>
       </c>
       <c r="E96">
-        <v>255.44</v>
+        <v>251.86</v>
       </c>
       <c r="F96">
-        <v>3626.37</v>
+        <v>3959.13</v>
       </c>
       <c r="G96">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -2762,22 +2761,22 @@
         </is>
       </c>
       <c r="B97">
-        <v>96678.36</v>
+        <v>94096.02</v>
       </c>
       <c r="C97">
-        <v>96678</v>
+        <v>434</v>
       </c>
       <c r="D97">
-        <v>1099.6</v>
+        <v>473.39</v>
       </c>
       <c r="E97">
-        <v>129.5</v>
+        <v>117.94</v>
       </c>
       <c r="F97">
-        <v>6647.25</v>
+        <v>3077.62</v>
       </c>
       <c r="G97">
-        <v>132</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98">
@@ -2787,22 +2786,22 @@
         </is>
       </c>
       <c r="B98">
-        <v>39868.47</v>
+        <v>23642.26</v>
       </c>
       <c r="C98">
-        <v>39868</v>
+        <v>147</v>
       </c>
       <c r="D98">
-        <v>76.34</v>
+        <v>55.06</v>
       </c>
       <c r="E98">
-        <v>172.33</v>
+        <v>122.66</v>
       </c>
       <c r="F98">
-        <v>876.16</v>
+        <v>490.64</v>
       </c>
       <c r="G98">
-        <v>171</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -2812,22 +2811,22 @@
         </is>
       </c>
       <c r="B99">
-        <v>372849.28</v>
+        <v>363218.35</v>
       </c>
       <c r="C99">
-        <v>372849</v>
+        <v>115</v>
       </c>
       <c r="D99">
-        <v>141.63</v>
+        <v>119.73</v>
       </c>
       <c r="E99">
-        <v>45.43</v>
+        <v>44.74</v>
       </c>
       <c r="F99">
-        <v>3504.8</v>
+        <v>3104.21</v>
       </c>
       <c r="G99">
-        <v>2973</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="100">
@@ -2837,22 +2836,22 @@
         </is>
       </c>
       <c r="B100">
-        <v>6821.78</v>
+        <v>14996.69</v>
       </c>
       <c r="C100">
-        <v>6822</v>
+        <v>300</v>
       </c>
       <c r="D100">
-        <v>148.84</v>
+        <v>220.68</v>
       </c>
       <c r="E100">
-        <v>52.75</v>
+        <v>103.54</v>
       </c>
       <c r="F100">
-        <v>552.98</v>
+        <v>885.34</v>
       </c>
       <c r="G100">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -2862,25 +2861,30 @@
         </is>
       </c>
       <c r="B101">
-        <v>241672.93</v>
+        <v>232185.13</v>
       </c>
       <c r="C101">
-        <v>241673</v>
+        <v>234</v>
       </c>
       <c r="D101">
-        <v>237.51</v>
+        <v>162.68</v>
       </c>
       <c r="E101">
-        <v>86.02</v>
+        <v>111.62</v>
       </c>
       <c r="F101">
-        <v>2803.26</v>
+        <v>1399.47</v>
       </c>
       <c r="G101">
-        <v>786</v>
+        <v>991</v>
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
+      </c>
       <c r="B102">
         <v>0</v>
       </c>
